--- a/车机软件汇总.xlsx
+++ b/车机软件汇总.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\自学编程\claude code\work3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6928F0A2-ED2F-4E41-853F-05406FABE63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68950A24-9354-4668-882B-D9F35CE7AAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1176" yWindow="0" windowWidth="19380" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="93">
   <si>
     <t>氢桌面普通版</t>
   </si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>切换到移动端页面再爬取</t>
@@ -321,6 +318,107 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>&lt;div class="service h-100 rcorners1"&gt;
+                        &lt;span class="wrap-icon"&gt;
+                            &lt;span class="icon-leaf"&gt;&lt;/span&gt;
+                        &lt;/span&gt;
+                        &lt;h4&gt;普通版本&lt;/h4&gt;
+                        &lt;h3&gt;V 1.8.4.7 (2026-03-13 17:30:34)&lt;/h3&gt;
+                        &lt;p&gt;
+                            支持车机:适合所有车机 &lt;br&gt; 支持功能: 悬浮地图, 不支持画中画                         &lt;/p&gt;
+                    &lt;/div&gt;，抓取普通版下载url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="service h-100 rcorners1"&gt;
+                        &lt;span class="wrap-icon"&gt;
+                            &lt;span class="icon-leaf"&gt;&lt;/span&gt;
+                        &lt;/span&gt;
+                        &lt;h4&gt;公签版本&lt;/h4&gt;
+                        &lt;h3&gt;V 1.8.4.7 (2026-03-13 17:29:56)&lt;/h3&gt;
+                        &lt;p&gt;
+                            支持车机:使用公共签名的车机:方易通车机,梁山车机,车连易盒子,领克E系列,吉利E系列.. &lt;br&gt; 支持功能: 支持画中画                         &lt;/p&gt;
+                    &lt;/div&gt;，抓取公签版下载url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="flex w-full space-x-[1.67vw]"&gt;&lt;a href="https://api.budingui.com/upgrade/download?key=69c659ff923659a5550da6a2&amp;amp;sign=21ef63ee8089b9dbe4c81840ef50e979" class="flex h-[2.8125vw] w-[11.46vw] cursor-pointer items-center justify-center space-x-[0.625vw] rounded-[0.52vw] text-[1.146vw] bg-[#25D9D0] text-black" aria-describedby=":Rmimqmqja:"&gt;&lt;span&gt;正式版下载&lt;/span&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" fill="none" version="1.1" width="24" height="24" viewBox="0 0 24 24" class="relative h-[1.25vw] w-[1.25vw]"&gt;&lt;defs&gt;&lt;clipPath id="master_svg0_166_4000"&gt;&lt;rect x="0" y="0" width="24" height="24" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;clipPath id="master_svg1_166_4003"&gt;&lt;rect x="19.579833984375" y="4.42095947265625" width="15.1578950881958" height="15.1578950881958" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;/defs&gt;&lt;g clip-path="url(#master_svg0_166_4000)"&gt;&lt;g&gt;&lt;g transform="matrix(0,1,-1,0,24.00079345703125,-15.15887451171875)" clip-path="url(#master_svg1_166_4003)"&gt;&lt;g&gt;&lt;path d="M27.814218,8.24305559765625Q27.674519,8.11518959765625,27.598197,7.94186659765625Q27.521875,7.76854459765625,27.521875,7.57916259765625Q27.521875,7.49052039765625,27.539168,7.40358159765625Q27.556462,7.31664259765625,27.590384,7.23474759765625Q27.624305,7.15285259765625,27.673553,7.07914959765625Q27.722799,7.00544659765625,27.785479,6.9427665976562505Q27.848159,6.88008659765625,27.921862,6.83083959765625Q27.995565,6.78159259765625,28.07746,6.74767159765625Q28.159355,6.71374959765625,28.246294,6.69645559765625Q28.3332328,6.67916259765625,28.421875,6.67916259765625Q28.611257,6.67916259765625,28.784579,6.75548459765625Q28.957902,6.83180659765625,29.085768,6.97150559765625L33.162915,11.04865259765625Q33.225535,11.11127259765625,33.274735,11.18490259765625Q33.323925,11.25853259765625,33.357815,11.34034259765625Q33.391705,11.42216259765625,33.408985,11.50901259765625Q33.426255,11.59587259765625,33.426255,11.684422597656251Q33.426255,11.772982597656249,33.408985,11.85983259765625Q33.391705,11.94669259765625,33.357815,12.02850259765625Q33.323925,12.11032259765625,33.274735,12.183952597656251Q33.225535,12.25758259765625,33.162915,12.32020259765625L29.085765,16.39735259765625Q28.957899,16.53704259765625,28.784578,16.61336259765625Q28.611256,16.68969259765625,28.421875,16.68969259765625Q28.3332328,16.68969259765625,28.246294,16.67239259765625Q28.159355,16.65510259765625,28.07746,16.62118259765625Q27.995565,16.58725259765625,27.921862,16.538012597656248Q27.848159,16.488762597656248,27.785479,16.42608259765625Q27.722799,16.36340259765625,27.673552,16.28970259765625Q27.624305,16.21600259765625,27.590384,16.134102597656252Q27.556462,16.05221259765625,27.539168,15.96527259765625Q27.521875,15.87833259765625,27.521875,15.78969259765625Q27.521875,15.60030259765625,27.598197,15.426982597656249Q27.67452,15.25366259765625,27.814219,15.12579259765625L31.255585,11.684422597656251L27.814218,8.24305559765625Z" fill-rule="evenodd" fill="black" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;g&gt;&lt;path d="M20.8829052484375,12.58326406640625Q20.8630321484375,12.58414306640625,20.8431396484375,12.58414306640625Q20.7544974484375,12.58414306640625,20.6675586484375,12.56685006640625Q20.5806196484375,12.54955606640625,20.4987246484375,12.51563406640625Q20.4168296484375,12.48171306640625,20.3431266484375,12.43246506640625Q20.2694236484375,12.38321906640625,20.2067436484375,12.32053906640625Q20.1440636484375,12.25785906640625,20.0948166484375,12.18415606640625Q20.0455696484375,12.11045306640625,20.0116486484375,12.02855806640625Q19.9777266484375,11.94666306640625,19.9604326484375,11.85972406640625Q19.9431396484375,11.77278526640625,19.9431396484375,11.68414306640625Q19.9431396484375,11.59550086640625,19.9604326484375,11.50856206640625Q19.9777266484375,11.42162306640625,20.0116486484375,11.33972806640625Q20.0455696484375,11.25783306640625,20.0948176484375,11.18413006640625Q20.1440636484375,11.11042706640625,20.2067436484375,11.04774706640625Q20.2694236484375,10.98506706640625,20.3431266484375,10.93582006640625Q20.4168296484375,10.88657306640625,20.4987246484375,10.85265206640625Q20.5806196484375,10.81873006640625,20.6675586484375,10.80143606640625Q20.7544974484375,10.78414306640625,20.8431396484375,10.78414306640625Q20.8630321484375,10.78414306640625,20.8829052484375,10.78502206640625L32.4875396484375,10.78502206640625Q32.5074396484375,10.78414306640625,32.527339648437504,10.78414306640625Q32.6160396484375,10.78414306640625,32.7029396484375,10.80143606640625Q32.7898396484375,10.81873006640625,32.8717396484375,10.85265206640625Q32.9536396484375,10.88657306640625,33.027339648437504,10.93582106640625Q33.1010396484375,10.98506706640625,33.1637396484375,11.04774706640625Q33.2264396484375,11.11042706640625,33.2756396484375,11.18413006640625Q33.3249396484375,11.25783306640625,33.3588396484375,11.33972806640625Q33.3927396484375,11.42162306640625,33.410039648437504,11.50856206640625Q33.427339648437496,11.59550086640625,33.427339648437496,11.68414306640625Q33.427339648437496,11.77278526640625,33.410039648437504,11.85972406640625Q33.3927396484375,11.94666306640625,33.3588396484375,12.02855806640625Q33.3249396484375,12.11045306640625,33.2756396484375,12.18415606640625Q33.2264396484375,12.25785906640625,33.1637396484375,12.32053906640625Q33.1010396484375,12.38321906640625,33.027339648437504,12.43246606640625Q32.9536396484375,12.48171306640625,32.8717396484375,12.51563406640625Q32.7898396484375,12.54955606640625,32.7029396484375,12.56685006640625Q32.6160396484375,12.58414306640625,32.527339648437504,12.58414306640625Q32.5074396484375,12.58414306640625,32.4875396484375,12.58326406640625L20.8829052484375,12.58326406640625Z" fill-rule="evenodd" fill="black" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;/g&gt;&lt;g&gt;&lt;ellipse cx="12.00027084350586" cy="11.99996566772461" rx="10.73684310913086" ry="10.73684310913086" fill-opacity="0" stroke-opacity="1" stroke="black" fill="none" stroke-width="1.558476448059082"&gt;&lt;/ellipse&gt;&lt;/g&gt;&lt;/g&gt;&lt;/g&gt;&lt;/svg&gt;&lt;/a&gt;&lt;div class="w-[11.46vw]"&gt;&lt;/div&gt;&lt;/div&gt;，抓取正式版下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a href="https://assets.autoshafa.com/apk/buding_bece53692609e838da3cd8e2d5cd9999_1.0.2.v4_V4webwww.apk" class="flex w-fit items-center justify-center text-center text-white/80" aria-describedby=":Rqimqmqja:"&gt;&lt;span class="mr-[0.5vw] border-b border-white/40 text-[0.74vw]"&gt;Android 4.x 系统&lt;/span&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" fill="none" version="1.1" width="24" height="24" viewBox="0 0 24 24" class="relative h-[1.04vw] w-[1.04vw]"&gt;&lt;defs&gt;&lt;clipPath id="master_svg0_166_4000"&gt;&lt;rect x="0" y="0" width="24" height="24" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;clipPath id="master_svg1_166_4003"&gt;&lt;rect x="19.579833984375" y="4.42095947265625" width="15.1578950881958" height="15.1578950881958" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;/defs&gt;&lt;g clip-path="url(#master_svg0_166_4000)"&gt;&lt;g&gt;&lt;g transform="matrix(0,1,-1,0,24.00079345703125,-15.15887451171875)" clip-path="url(#master_svg1_166_4003)"&gt;&lt;g&gt;&lt;path d="M27.814218,8.24305559765625Q27.674519,8.11518959765625,27.598197,7.94186659765625Q27.521875,7.76854459765625,27.521875,7.57916259765625Q27.521875,7.49052039765625,27.539168,7.40358159765625Q27.556462,7.31664259765625,27.590384,7.23474759765625Q27.624305,7.15285259765625,27.673553,7.07914959765625Q27.722799,7.00544659765625,27.785479,6.9427665976562505Q27.848159,6.88008659765625,27.921862,6.83083959765625Q27.995565,6.78159259765625,28.07746,6.74767159765625Q28.159355,6.71374959765625,28.246294,6.69645559765625Q28.3332328,6.67916259765625,28.421875,6.67916259765625Q28.611257,6.67916259765625,28.784579,6.75548459765625Q28.957902,6.83180659765625,29.085768,6.97150559765625L33.162915,11.04865259765625Q33.225535,11.11127259765625,33.274735,11.18490259765625Q33.323925,11.25853259765625,33.357815,11.34034259765625Q33.391705,11.42216259765625,33.408985,11.50901259765625Q33.426255,11.59587259765625,33.426255,11.684422597656251Q33.426255,11.772982597656249,33.408985,11.85983259765625Q33.391705,11.94669259765625,33.357815,12.02850259765625Q33.323925,12.11032259765625,33.274735,12.183952597656251Q33.225535,12.25758259765625,33.162915,12.32020259765625L29.085765,16.39735259765625Q28.957899,16.53704259765625,28.784578,16.61336259765625Q28.611256,16.68969259765625,28.421875,16.68969259765625Q28.3332328,16.68969259765625,28.246294,16.67239259765625Q28.159355,16.65510259765625,28.07746,16.62118259765625Q27.995565,16.58725259765625,27.921862,16.538012597656248Q27.848159,16.488762597656248,27.785479,16.42608259765625Q27.722799,16.36340259765625,27.673552,16.28970259765625Q27.624305,16.21600259765625,27.590384,16.134102597656252Q27.556462,16.05221259765625,27.539168,15.96527259765625Q27.521875,15.87833259765625,27.521875,15.78969259765625Q27.521875,15.60030259765625,27.598197,15.426982597656249Q27.67452,15.25366259765625,27.814219,15.12579259765625L31.255585,11.684422597656251L27.814218,8.24305559765625Z" fill-rule="evenodd" fill="rgba(255,255,255,0.8)" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;g&gt;&lt;path d="M20.8829052484375,12.58326406640625Q20.8630321484375,12.58414306640625,20.8431396484375,12.58414306640625Q20.7544974484375,12.58414306640625,20.6675586484375,12.56685006640625Q20.5806196484375,12.54955606640625,20.4987246484375,12.51563406640625Q20.4168296484375,12.48171306640625,20.3431266484375,12.43246506640625Q20.2694236484375,12.38321906640625,20.2067436484375,12.32053906640625Q20.1440636484375,12.25785906640625,20.0948166484375,12.18415606640625Q20.0455696484375,12.11045306640625,20.0116486484375,12.02855806640625Q19.9777266484375,11.94666306640625,19.9604326484375,11.85972406640625Q19.9431396484375,11.77278526640625,19.9431396484375,11.68414306640625Q19.9431396484375,11.59550086640625,19.9604326484375,11.50856206640625Q19.9777266484375,11.42162306640625,20.0116486484375,11.33972806640625Q20.0455696484375,11.25783306640625,20.0948176484375,11.18413006640625Q20.1440636484375,11.11042706640625,20.2067436484375,11.04774706640625Q20.2694236484375,10.98506706640625,20.3431266484375,10.93582006640625Q20.4168296484375,10.88657306640625,20.4987246484375,10.85265206640625Q20.5806196484375,10.81873006640625,20.6675586484375,10.80143606640625Q20.7544974484375,10.78414306640625,20.8431396484375,10.78414306640625Q20.8630321484375,10.78414306640625,20.8829052484375,10.78502206640625L32.4875396484375,10.78502206640625Q32.5074396484375,10.78414306640625,32.527339648437504,10.78414306640625Q32.6160396484375,10.78414306640625,32.7029396484375,10.80143606640625Q32.7898396484375,10.81873006640625,32.8717396484375,10.85265206640625Q32.9536396484375,10.88657306640625,33.027339648437504,10.93582106640625Q33.1010396484375,10.98506706640625,33.1637396484375,11.04774706640625Q33.2264396484375,11.11042706640625,33.2756396484375,11.18413006640625Q33.3249396484375,11.25783306640625,33.3588396484375,11.33972806640625Q33.3927396484375,11.42162306640625,33.410039648437504,11.50856206640625Q33.427339648437496,11.59550086640625,33.427339648437496,11.68414306640625Q33.427339648437496,11.77278526640625,33.410039648437504,11.85972406640625Q33.3927396484375,11.94666306640625,33.3588396484375,12.02855806640625Q33.3249396484375,12.11045306640625,33.2756396484375,12.18415606640625Q33.2264396484375,12.25785906640625,33.1637396484375,12.32053906640625Q33.1010396484375,12.38321906640625,33.027339648437504,12.43246606640625Q32.9536396484375,12.48171306640625,32.8717396484375,12.51563406640625Q32.7898396484375,12.54955606640625,32.7029396484375,12.56685006640625Q32.6160396484375,12.58414306640625,32.527339648437504,12.58414306640625Q32.5074396484375,12.58414306640625,32.4875396484375,12.58326406640625L20.8829052484375,12.58326406640625Z" fill-rule="evenodd" fill="rgba(255,255,255,0.8)" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;/g&gt;&lt;g&gt;&lt;ellipse cx="12.00027084350586" cy="11.99996566772461" rx="10.73684310913086" ry="10.73684310913086" fill-opacity="0" stroke-opacity="1" stroke="rgba(255,255,255,0.8)" fill="none" stroke-width="1.558476448059082"&gt;&lt;/ellipse&gt;&lt;/g&gt;&lt;/g&gt;&lt;/g&gt;&lt;/svg&gt;&lt;/a&gt;，抓取android 4.x 版下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;button class="channel-card active" data-channel="normal" data-description="普通签名版本"&gt;
+            &lt;div class="card-icon" style="background: linear-gradient(135deg, #007aff 0%, #0051d5 100%); box-shadow: 0 4px 12px rgba(0, 122, 255, 0.35);"&gt;
+                &lt;i class="fas fa-star"&gt;&lt;/i&gt;
+            &lt;/div&gt;
+            &lt;div class="card-info"&gt;
+                &lt;h4&gt;公众版&lt;/h4&gt;
+            &lt;/div&gt;
+            &lt;div class="card-check"&gt;
+                &lt;i class="fas fa-check-circle"&gt;&lt;/i&gt;
+            &lt;/div&gt;
+        &lt;/button&gt;，抓取公众版的下载url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;button class="channel-card active" data-channel="platform" data-description="Android公版签名"&gt;
+            &lt;div class="card-icon" style="background: linear-gradient(135deg, #3ddc84 0%, #1ea85a 100%); box-shadow: 0 4px 12px rgba(61, 220, 132, 0.4);"&gt;
+                &lt;i class="fas fa-cogs"&gt;&lt;/i&gt;
+            &lt;/div&gt;
+            &lt;div class="card-info"&gt;
+                &lt;h4&gt;AOSP&lt;/h4&gt;
+            &lt;/div&gt;
+            &lt;div class="card-check"&gt;
+                &lt;i class="fas fa-check-circle"&gt;&lt;/i&gt;
+            &lt;/div&gt;
+        &lt;/button&gt;，抓取aosp的下载url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a href="https://mapdownload.autonavi.com/apps/auto/manual/V910/Auto_9.1.0.600087_release_signed.apk?u=98c348d92dd62ab6caaf7d622c9c35b7&amp;amp;" target="_blank" class="download_btn" onclick="_czc.push(['_trackEvent', '产品下载-APP下载', '点击', '产品下载-APP下载-2.0.0车机版下载']);"&gt;立即下载&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;img data-v-9965eb0e="" src="https://map-mobile-resource.cdn.bcebos.com/icon/service/avn-handcart/default/acv21-btn-b.png" class="btn-img"&gt;，点击事件，点击开始下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;button data-v-3fbe776b="" class="global-button"&gt;立即下载&lt;/button&gt;，点击事件，点击开始下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="item item0" data-v-3d1eb8a0=""&gt;&lt;div class="icon" data-v-3d1eb8a0=""&gt;&lt;i class="icon_car" data-v-3d1eb8a0=""&gt;&lt;/i&gt;&lt;/div&gt; &lt;div class="text" data-v-3d1eb8a0=""&gt;&lt;p class="type" data-v-3d1eb8a0=""&gt;车载公版&lt;/p&gt; &lt;p data-v-3d1eb8a0=""&gt;立即下载&lt;/p&gt;&lt;/div&gt;&lt;/div&gt;，点击事件，点击后开始下载抓取车载公版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="item item4" data-v-3d1eb8a0=""&gt;&lt;div class="icon" data-v-3d1eb8a0=""&gt;&lt;i class="icon_car" data-v-3d1eb8a0=""&gt;&lt;/i&gt;&lt;/div&gt; &lt;div class="text" data-v-3d1eb8a0=""&gt;&lt;p class="type" data-v-3d1eb8a0=""&gt;车载极简版&lt;/p&gt; &lt;p data-v-3d1eb8a0=""&gt;立即下载&lt;/p&gt;&lt;/div&gt;&lt;/div&gt;，点击事件，点击后开始下载抓取车载极简版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="tuijian_product_other_item  mr_20 clear_fix fl"&gt;
+                        &lt;a style="background:url(https://imge.kugou.com/commendpic/20250513/20250513195547550860.png) no-repeat center center" hidefocus="true" href="/dl/kugou_auto" target="_blank" title="酷狗音乐 车载版" title2="kugou_auto" class=" fl icon_img"&gt;酷狗音乐 车载版&lt;/a&gt;
+            &lt;p class="tuijian_product_other_description fl"&gt;
+                &lt;a hidefocus="true" href="/dl/kugou_auto" target="_blank" title="酷狗音乐 车载版" class="tuijian_product_title"&gt;酷狗音乐 车载版&lt;/a&gt;
+                    &lt;span class="tuijian_product_version"&gt;更新日期：2026-01-26&lt;/span&gt;
+            &lt;/p&gt;
+            &lt;div class="tuijian_product_other_download"&gt;&lt;a hidefocus="true" target="_blank" onclick="phpLogClick(1287);" title="下载酷狗音乐 车载版" title2="kugou_auto" href="/dl/kugou_auto" class="tuijian_product_download"&gt;下载&lt;/a&gt;
+                   &lt;span class="tuijian_product_other_version"&gt;6.1.0&lt;/span&gt;
+            &lt;/div&gt;
+                    &lt;/div&gt;，抓取车载版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先点击&lt;a href="a"&gt;立即下载&lt;/a&gt;，弹出&lt;div class="download-confirm download-confirm-click-header"&gt;&lt;div class="download-confirm-title"&gt;下载提示&lt;/div&gt;&lt;div class="download-confirm-content"&gt;该应用车机版本为公版，仅限个人用户消费使用，不可用于商业服务用途，对于违规使用产生的后果及风险，喜马拉雅保留追究责任的权利。&lt;/div&gt;&lt;div class="download-confirm-button"&gt;&lt;a href="https://apk.pcdn.xmcdn.com/storages/445c-audiofreehighqps/23/BA/GAqhntANMAkfAro9NQRS9RuR.apk" class="download-confirm-agree" id="ximalaya"&gt;确认并下载&lt;/a&gt;&lt;div class="download-confirm-disagree"&gt;取消&lt;/div&gt;&lt;/div&gt;&lt;/div&gt;，再点击&lt;a href="https://apk.pcdn.xmcdn.com/storages/445c-audiofreehighqps/23/BA/GAqhntANMAkfAro9NQRS9RuR.apk" class="download-confirm-agree" id="ximalaya"&gt;确认并下载&lt;/a&gt; 开始下载。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a href="https://dl.hdslb.com/mobile/latest/android_bilithings_super/bilithings-master.apk?t=20260418" target="_blank" class="dt-btn btn-car bg-car" data-type="car" title="车机版"&gt;&lt;/a&gt;，抓取车载版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>点击下载，进行html解析，右上角&lt;a class="btn" onclick="showdownload()"&gt;下载&lt;/a&gt; 点击之后，出现这个dialog&lt;div class="download_dialog_con" onclick="window.event.cancelBubble = true;" style="overflow:auto;padding-left:20px;"&gt;
                 &lt;center&gt;
                     &lt;div style="color:#999;font-size:12px;"&gt;
@@ -361,79 +459,7 @@
                         &lt;/a&gt;
                     &lt;/div&gt;
                 &lt;/center&gt;
-            &lt;/div&gt;，然后解析dialog内部的结构，每个a标签的href就是下载的链接，然后画中画版下面抓取公签版下载的url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="service h-100 rcorners1"&gt;
-                        &lt;span class="wrap-icon"&gt;
-                            &lt;span class="icon-leaf"&gt;&lt;/span&gt;
-                        &lt;/span&gt;
-                        &lt;h4&gt;普通版本&lt;/h4&gt;
-                        &lt;h3&gt;V 1.8.4.7 (2026-03-13 17:30:34)&lt;/h3&gt;
-                        &lt;p&gt;
-                            支持车机:适合所有车机 &lt;br&gt; 支持功能: 悬浮地图, 不支持画中画                         &lt;/p&gt;
-                    &lt;/div&gt;，抓取普通版下载url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="service h-100 rcorners1"&gt;
-                        &lt;span class="wrap-icon"&gt;
-                            &lt;span class="icon-leaf"&gt;&lt;/span&gt;
-                        &lt;/span&gt;
-                        &lt;h4&gt;公签版本&lt;/h4&gt;
-                        &lt;h3&gt;V 1.8.4.7 (2026-03-13 17:29:56)&lt;/h3&gt;
-                        &lt;p&gt;
-                            支持车机:使用公共签名的车机:方易通车机,梁山车机,车连易盒子,领克E系列,吉利E系列.. &lt;br&gt; 支持功能: 支持画中画                         &lt;/p&gt;
-                    &lt;/div&gt;，抓取公签版下载url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="flex w-full space-x-[1.67vw]"&gt;&lt;a href="https://api.budingui.com/upgrade/download?key=69c659ff923659a5550da6a2&amp;amp;sign=21ef63ee8089b9dbe4c81840ef50e979" class="flex h-[2.8125vw] w-[11.46vw] cursor-pointer items-center justify-center space-x-[0.625vw] rounded-[0.52vw] text-[1.146vw] bg-[#25D9D0] text-black" aria-describedby=":Rmimqmqja:"&gt;&lt;span&gt;正式版下载&lt;/span&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" fill="none" version="1.1" width="24" height="24" viewBox="0 0 24 24" class="relative h-[1.25vw] w-[1.25vw]"&gt;&lt;defs&gt;&lt;clipPath id="master_svg0_166_4000"&gt;&lt;rect x="0" y="0" width="24" height="24" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;clipPath id="master_svg1_166_4003"&gt;&lt;rect x="19.579833984375" y="4.42095947265625" width="15.1578950881958" height="15.1578950881958" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;/defs&gt;&lt;g clip-path="url(#master_svg0_166_4000)"&gt;&lt;g&gt;&lt;g transform="matrix(0,1,-1,0,24.00079345703125,-15.15887451171875)" clip-path="url(#master_svg1_166_4003)"&gt;&lt;g&gt;&lt;path d="M27.814218,8.24305559765625Q27.674519,8.11518959765625,27.598197,7.94186659765625Q27.521875,7.76854459765625,27.521875,7.57916259765625Q27.521875,7.49052039765625,27.539168,7.40358159765625Q27.556462,7.31664259765625,27.590384,7.23474759765625Q27.624305,7.15285259765625,27.673553,7.07914959765625Q27.722799,7.00544659765625,27.785479,6.9427665976562505Q27.848159,6.88008659765625,27.921862,6.83083959765625Q27.995565,6.78159259765625,28.07746,6.74767159765625Q28.159355,6.71374959765625,28.246294,6.69645559765625Q28.3332328,6.67916259765625,28.421875,6.67916259765625Q28.611257,6.67916259765625,28.784579,6.75548459765625Q28.957902,6.83180659765625,29.085768,6.97150559765625L33.162915,11.04865259765625Q33.225535,11.11127259765625,33.274735,11.18490259765625Q33.323925,11.25853259765625,33.357815,11.34034259765625Q33.391705,11.42216259765625,33.408985,11.50901259765625Q33.426255,11.59587259765625,33.426255,11.684422597656251Q33.426255,11.772982597656249,33.408985,11.85983259765625Q33.391705,11.94669259765625,33.357815,12.02850259765625Q33.323925,12.11032259765625,33.274735,12.183952597656251Q33.225535,12.25758259765625,33.162915,12.32020259765625L29.085765,16.39735259765625Q28.957899,16.53704259765625,28.784578,16.61336259765625Q28.611256,16.68969259765625,28.421875,16.68969259765625Q28.3332328,16.68969259765625,28.246294,16.67239259765625Q28.159355,16.65510259765625,28.07746,16.62118259765625Q27.995565,16.58725259765625,27.921862,16.538012597656248Q27.848159,16.488762597656248,27.785479,16.42608259765625Q27.722799,16.36340259765625,27.673552,16.28970259765625Q27.624305,16.21600259765625,27.590384,16.134102597656252Q27.556462,16.05221259765625,27.539168,15.96527259765625Q27.521875,15.87833259765625,27.521875,15.78969259765625Q27.521875,15.60030259765625,27.598197,15.426982597656249Q27.67452,15.25366259765625,27.814219,15.12579259765625L31.255585,11.684422597656251L27.814218,8.24305559765625Z" fill-rule="evenodd" fill="black" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;g&gt;&lt;path d="M20.8829052484375,12.58326406640625Q20.8630321484375,12.58414306640625,20.8431396484375,12.58414306640625Q20.7544974484375,12.58414306640625,20.6675586484375,12.56685006640625Q20.5806196484375,12.54955606640625,20.4987246484375,12.51563406640625Q20.4168296484375,12.48171306640625,20.3431266484375,12.43246506640625Q20.2694236484375,12.38321906640625,20.2067436484375,12.32053906640625Q20.1440636484375,12.25785906640625,20.0948166484375,12.18415606640625Q20.0455696484375,12.11045306640625,20.0116486484375,12.02855806640625Q19.9777266484375,11.94666306640625,19.9604326484375,11.85972406640625Q19.9431396484375,11.77278526640625,19.9431396484375,11.68414306640625Q19.9431396484375,11.59550086640625,19.9604326484375,11.50856206640625Q19.9777266484375,11.42162306640625,20.0116486484375,11.33972806640625Q20.0455696484375,11.25783306640625,20.0948176484375,11.18413006640625Q20.1440636484375,11.11042706640625,20.2067436484375,11.04774706640625Q20.2694236484375,10.98506706640625,20.3431266484375,10.93582006640625Q20.4168296484375,10.88657306640625,20.4987246484375,10.85265206640625Q20.5806196484375,10.81873006640625,20.6675586484375,10.80143606640625Q20.7544974484375,10.78414306640625,20.8431396484375,10.78414306640625Q20.8630321484375,10.78414306640625,20.8829052484375,10.78502206640625L32.4875396484375,10.78502206640625Q32.5074396484375,10.78414306640625,32.527339648437504,10.78414306640625Q32.6160396484375,10.78414306640625,32.7029396484375,10.80143606640625Q32.7898396484375,10.81873006640625,32.8717396484375,10.85265206640625Q32.9536396484375,10.88657306640625,33.027339648437504,10.93582106640625Q33.1010396484375,10.98506706640625,33.1637396484375,11.04774706640625Q33.2264396484375,11.11042706640625,33.2756396484375,11.18413006640625Q33.3249396484375,11.25783306640625,33.3588396484375,11.33972806640625Q33.3927396484375,11.42162306640625,33.410039648437504,11.50856206640625Q33.427339648437496,11.59550086640625,33.427339648437496,11.68414306640625Q33.427339648437496,11.77278526640625,33.410039648437504,11.85972406640625Q33.3927396484375,11.94666306640625,33.3588396484375,12.02855806640625Q33.3249396484375,12.11045306640625,33.2756396484375,12.18415606640625Q33.2264396484375,12.25785906640625,33.1637396484375,12.32053906640625Q33.1010396484375,12.38321906640625,33.027339648437504,12.43246606640625Q32.9536396484375,12.48171306640625,32.8717396484375,12.51563406640625Q32.7898396484375,12.54955606640625,32.7029396484375,12.56685006640625Q32.6160396484375,12.58414306640625,32.527339648437504,12.58414306640625Q32.5074396484375,12.58414306640625,32.4875396484375,12.58326406640625L20.8829052484375,12.58326406640625Z" fill-rule="evenodd" fill="black" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;/g&gt;&lt;g&gt;&lt;ellipse cx="12.00027084350586" cy="11.99996566772461" rx="10.73684310913086" ry="10.73684310913086" fill-opacity="0" stroke-opacity="1" stroke="black" fill="none" stroke-width="1.558476448059082"&gt;&lt;/ellipse&gt;&lt;/g&gt;&lt;/g&gt;&lt;/g&gt;&lt;/svg&gt;&lt;/a&gt;&lt;div class="w-[11.46vw]"&gt;&lt;/div&gt;&lt;/div&gt;，抓取正式版下载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a href="https://assets.autoshafa.com/apk/buding_bece53692609e838da3cd8e2d5cd9999_1.0.2.v4_V4webwww.apk" class="flex w-fit items-center justify-center text-center text-white/80" aria-describedby=":Rqimqmqja:"&gt;&lt;span class="mr-[0.5vw] border-b border-white/40 text-[0.74vw]"&gt;Android 4.x 系统&lt;/span&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" fill="none" version="1.1" width="24" height="24" viewBox="0 0 24 24" class="relative h-[1.04vw] w-[1.04vw]"&gt;&lt;defs&gt;&lt;clipPath id="master_svg0_166_4000"&gt;&lt;rect x="0" y="0" width="24" height="24" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;clipPath id="master_svg1_166_4003"&gt;&lt;rect x="19.579833984375" y="4.42095947265625" width="15.1578950881958" height="15.1578950881958" rx="0"&gt;&lt;/rect&gt;&lt;/clipPath&gt;&lt;/defs&gt;&lt;g clip-path="url(#master_svg0_166_4000)"&gt;&lt;g&gt;&lt;g transform="matrix(0,1,-1,0,24.00079345703125,-15.15887451171875)" clip-path="url(#master_svg1_166_4003)"&gt;&lt;g&gt;&lt;path d="M27.814218,8.24305559765625Q27.674519,8.11518959765625,27.598197,7.94186659765625Q27.521875,7.76854459765625,27.521875,7.57916259765625Q27.521875,7.49052039765625,27.539168,7.40358159765625Q27.556462,7.31664259765625,27.590384,7.23474759765625Q27.624305,7.15285259765625,27.673553,7.07914959765625Q27.722799,7.00544659765625,27.785479,6.9427665976562505Q27.848159,6.88008659765625,27.921862,6.83083959765625Q27.995565,6.78159259765625,28.07746,6.74767159765625Q28.159355,6.71374959765625,28.246294,6.69645559765625Q28.3332328,6.67916259765625,28.421875,6.67916259765625Q28.611257,6.67916259765625,28.784579,6.75548459765625Q28.957902,6.83180659765625,29.085768,6.97150559765625L33.162915,11.04865259765625Q33.225535,11.11127259765625,33.274735,11.18490259765625Q33.323925,11.25853259765625,33.357815,11.34034259765625Q33.391705,11.42216259765625,33.408985,11.50901259765625Q33.426255,11.59587259765625,33.426255,11.684422597656251Q33.426255,11.772982597656249,33.408985,11.85983259765625Q33.391705,11.94669259765625,33.357815,12.02850259765625Q33.323925,12.11032259765625,33.274735,12.183952597656251Q33.225535,12.25758259765625,33.162915,12.32020259765625L29.085765,16.39735259765625Q28.957899,16.53704259765625,28.784578,16.61336259765625Q28.611256,16.68969259765625,28.421875,16.68969259765625Q28.3332328,16.68969259765625,28.246294,16.67239259765625Q28.159355,16.65510259765625,28.07746,16.62118259765625Q27.995565,16.58725259765625,27.921862,16.538012597656248Q27.848159,16.488762597656248,27.785479,16.42608259765625Q27.722799,16.36340259765625,27.673552,16.28970259765625Q27.624305,16.21600259765625,27.590384,16.134102597656252Q27.556462,16.05221259765625,27.539168,15.96527259765625Q27.521875,15.87833259765625,27.521875,15.78969259765625Q27.521875,15.60030259765625,27.598197,15.426982597656249Q27.67452,15.25366259765625,27.814219,15.12579259765625L31.255585,11.684422597656251L27.814218,8.24305559765625Z" fill-rule="evenodd" fill="rgba(255,255,255,0.8)" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;g&gt;&lt;path d="M20.8829052484375,12.58326406640625Q20.8630321484375,12.58414306640625,20.8431396484375,12.58414306640625Q20.7544974484375,12.58414306640625,20.6675586484375,12.56685006640625Q20.5806196484375,12.54955606640625,20.4987246484375,12.51563406640625Q20.4168296484375,12.48171306640625,20.3431266484375,12.43246506640625Q20.2694236484375,12.38321906640625,20.2067436484375,12.32053906640625Q20.1440636484375,12.25785906640625,20.0948166484375,12.18415606640625Q20.0455696484375,12.11045306640625,20.0116486484375,12.02855806640625Q19.9777266484375,11.94666306640625,19.9604326484375,11.85972406640625Q19.9431396484375,11.77278526640625,19.9431396484375,11.68414306640625Q19.9431396484375,11.59550086640625,19.9604326484375,11.50856206640625Q19.9777266484375,11.42162306640625,20.0116486484375,11.33972806640625Q20.0455696484375,11.25783306640625,20.0948176484375,11.18413006640625Q20.1440636484375,11.11042706640625,20.2067436484375,11.04774706640625Q20.2694236484375,10.98506706640625,20.3431266484375,10.93582006640625Q20.4168296484375,10.88657306640625,20.4987246484375,10.85265206640625Q20.5806196484375,10.81873006640625,20.6675586484375,10.80143606640625Q20.7544974484375,10.78414306640625,20.8431396484375,10.78414306640625Q20.8630321484375,10.78414306640625,20.8829052484375,10.78502206640625L32.4875396484375,10.78502206640625Q32.5074396484375,10.78414306640625,32.527339648437504,10.78414306640625Q32.6160396484375,10.78414306640625,32.7029396484375,10.80143606640625Q32.7898396484375,10.81873006640625,32.8717396484375,10.85265206640625Q32.9536396484375,10.88657306640625,33.027339648437504,10.93582106640625Q33.1010396484375,10.98506706640625,33.1637396484375,11.04774706640625Q33.2264396484375,11.11042706640625,33.2756396484375,11.18413006640625Q33.3249396484375,11.25783306640625,33.3588396484375,11.33972806640625Q33.3927396484375,11.42162306640625,33.410039648437504,11.50856206640625Q33.427339648437496,11.59550086640625,33.427339648437496,11.68414306640625Q33.427339648437496,11.77278526640625,33.410039648437504,11.85972406640625Q33.3927396484375,11.94666306640625,33.3588396484375,12.02855806640625Q33.3249396484375,12.11045306640625,33.2756396484375,12.18415606640625Q33.2264396484375,12.25785906640625,33.1637396484375,12.32053906640625Q33.1010396484375,12.38321906640625,33.027339648437504,12.43246606640625Q32.9536396484375,12.48171306640625,32.8717396484375,12.51563406640625Q32.7898396484375,12.54955606640625,32.7029396484375,12.56685006640625Q32.6160396484375,12.58414306640625,32.527339648437504,12.58414306640625Q32.5074396484375,12.58414306640625,32.4875396484375,12.58326406640625L20.8829052484375,12.58326406640625Z" fill-rule="evenodd" fill="rgba(255,255,255,0.8)" fill-opacity="1"&gt;&lt;/path&gt;&lt;/g&gt;&lt;/g&gt;&lt;g&gt;&lt;ellipse cx="12.00027084350586" cy="11.99996566772461" rx="10.73684310913086" ry="10.73684310913086" fill-opacity="0" stroke-opacity="1" stroke="rgba(255,255,255,0.8)" fill="none" stroke-width="1.558476448059082"&gt;&lt;/ellipse&gt;&lt;/g&gt;&lt;/g&gt;&lt;/g&gt;&lt;/svg&gt;&lt;/a&gt;，抓取android 4.x 版下载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;button class="channel-card active" data-channel="normal" data-description="普通签名版本"&gt;
-            &lt;div class="card-icon" style="background: linear-gradient(135deg, #007aff 0%, #0051d5 100%); box-shadow: 0 4px 12px rgba(0, 122, 255, 0.35);"&gt;
-                &lt;i class="fas fa-star"&gt;&lt;/i&gt;
-            &lt;/div&gt;
-            &lt;div class="card-info"&gt;
-                &lt;h4&gt;公众版&lt;/h4&gt;
-            &lt;/div&gt;
-            &lt;div class="card-check"&gt;
-                &lt;i class="fas fa-check-circle"&gt;&lt;/i&gt;
-            &lt;/div&gt;
-        &lt;/button&gt;，抓取公众版的下载url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;button class="channel-card active" data-channel="platform" data-description="Android公版签名"&gt;
-            &lt;div class="card-icon" style="background: linear-gradient(135deg, #3ddc84 0%, #1ea85a 100%); box-shadow: 0 4px 12px rgba(61, 220, 132, 0.4);"&gt;
-                &lt;i class="fas fa-cogs"&gt;&lt;/i&gt;
-            &lt;/div&gt;
-            &lt;div class="card-info"&gt;
-                &lt;h4&gt;AOSP&lt;/h4&gt;
-            &lt;/div&gt;
-            &lt;div class="card-check"&gt;
-                &lt;i class="fas fa-check-circle"&gt;&lt;/i&gt;
-            &lt;/div&gt;
-        &lt;/button&gt;，抓取aosp的下载url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a href="https://mapdownload.autonavi.com/apps/auto/manual/V910/Auto_9.1.0.600087_release_signed.apk?u=98c348d92dd62ab6caaf7d622c9c35b7&amp;amp;" target="_blank" class="download_btn" onclick="_czc.push(['_trackEvent', '产品下载-APP下载', '点击', '产品下载-APP下载-2.0.0车机版下载']);"&gt;立即下载&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;img data-v-9965eb0e="" src="https://map-mobile-resource.cdn.bcebos.com/icon/service/avn-handcart/default/acv21-btn-b.png" class="btn-img"&gt;，点击事件，点击开始下载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;button data-v-3fbe776b="" class="global-button"&gt;立即下载&lt;/button&gt;，点击事件，点击开始下载</t>
+            &lt;/div&gt;，然后解析dialog内部的结构，每个a标签的href就是下载的链接，然后画中画版下面，也就是这里&lt;a id="" class="down_btn down_gq_hzh" target="_blank" href="https://vv.hyjidi.com/app/122/画中画公签版1.apk"&gt;公签版&lt;/a&gt;，抓取公签版下载的url</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -466,44 +492,101 @@
                                     &lt;li class="version_list__item" title=" 发布时间：2026-04-03"&gt;-  发布时间：2026-04-03&lt;/li&gt;
                         &lt;/ul&gt;
                         &lt;a class="product__btn js_show_tips" data-type="10" href="javascript:;"&gt;下载&lt;/a&gt;
-                    &lt;/li&gt;，抓取Android 车载的下载url</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="item item0" data-v-3d1eb8a0=""&gt;&lt;div class="icon" data-v-3d1eb8a0=""&gt;&lt;i class="icon_car" data-v-3d1eb8a0=""&gt;&lt;/i&gt;&lt;/div&gt; &lt;div class="text" data-v-3d1eb8a0=""&gt;&lt;p class="type" data-v-3d1eb8a0=""&gt;车载公版&lt;/p&gt; &lt;p data-v-3d1eb8a0=""&gt;立即下载&lt;/p&gt;&lt;/div&gt;&lt;/div&gt;，点击事件，点击后开始下载抓取车载公版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="item item4" data-v-3d1eb8a0=""&gt;&lt;div class="icon" data-v-3d1eb8a0=""&gt;&lt;i class="icon_car" data-v-3d1eb8a0=""&gt;&lt;/i&gt;&lt;/div&gt; &lt;div class="text" data-v-3d1eb8a0=""&gt;&lt;p class="type" data-v-3d1eb8a0=""&gt;车载极简版&lt;/p&gt; &lt;p data-v-3d1eb8a0=""&gt;立即下载&lt;/p&gt;&lt;/div&gt;&lt;/div&gt;，点击事件，点击后开始下载抓取车载极简版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;div class="tuijian_product_other_item  mr_20 clear_fix fl"&gt;
-                        &lt;a style="background:url(https://imge.kugou.com/commendpic/20250513/20250513195547550860.png) no-repeat center center" hidefocus="true" href="/dl/kugou_auto" target="_blank" title="酷狗音乐 车载版" title2="kugou_auto" class=" fl icon_img"&gt;酷狗音乐 车载版&lt;/a&gt;
-            &lt;p class="tuijian_product_other_description fl"&gt;
-                &lt;a hidefocus="true" href="/dl/kugou_auto" target="_blank" title="酷狗音乐 车载版" class="tuijian_product_title"&gt;酷狗音乐 车载版&lt;/a&gt;
-                    &lt;span class="tuijian_product_version"&gt;更新日期：2026-01-26&lt;/span&gt;
-            &lt;/p&gt;
-            &lt;div class="tuijian_product_other_download"&gt;&lt;a hidefocus="true" target="_blank" onclick="phpLogClick(1287);" title="下载酷狗音乐 车载版" title2="kugou_auto" href="/dl/kugou_auto" class="tuijian_product_download"&gt;下载&lt;/a&gt;
-                   &lt;span class="tuijian_product_other_version"&gt;6.1.0&lt;/span&gt;
+                    &lt;/li&gt;，点击之后会弹出一个dialog，&lt;div class="popup_dialog"&gt;
+            &lt;div class="popup_dialog_hd"&gt;
+                &lt;button type="button" aria-label="Close" class="yqq-dialog-close"&gt;&lt;span class="yqq-dialog-close-x"&gt;&lt;/span&gt;&lt;/button&gt;
             &lt;/div&gt;
-                    &lt;/div&gt;，抓取车载版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先点击&lt;a href="a"&gt;立即下载&lt;/a&gt;，弹出&lt;div class="download-confirm download-confirm-click-header"&gt;&lt;div class="download-confirm-title"&gt;下载提示&lt;/div&gt;&lt;div class="download-confirm-content"&gt;该应用车机版本为公版，仅限个人用户消费使用，不可用于商业服务用途，对于违规使用产生的后果及风险，喜马拉雅保留追究责任的权利。&lt;/div&gt;&lt;div class="download-confirm-button"&gt;&lt;a href="https://apk.pcdn.xmcdn.com/storages/445c-audiofreehighqps/23/BA/GAqhntANMAkfAro9NQRS9RuR.apk" class="download-confirm-agree" id="ximalaya"&gt;确认并下载&lt;/a&gt;&lt;div class="download-confirm-disagree"&gt;取消&lt;/div&gt;&lt;/div&gt;&lt;/div&gt;，再点击&lt;a href="https://apk.pcdn.xmcdn.com/storages/445c-audiofreehighqps/23/BA/GAqhntANMAkfAro9NQRS9RuR.apk" class="download-confirm-agree" id="ximalaya"&gt;确认并下载&lt;/a&gt; 开始下载。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a href="https://dl.hdslb.com/mobile/latest/android_bilithings_super/bilithings-master.apk?t=20260418" target="_blank" class="dt-btn btn-car bg-car" data-type="car" title="车机版"&gt;&lt;/a&gt;，抓取车载版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+            &lt;div class="popup_dialog_cont popup_dowload_cont"&gt;&lt;div class="popup__hd"&gt;&lt;h2 class="popup__tit"&gt;下载提示&lt;/h2&gt;&lt;/div&gt;&lt;div class="popup__bd"&gt;&lt;div class="popup__bd_inner"&gt;&lt;h3 class="popup__subtit popup__subtit--single" style="white-space:inherit;"&gt;该车机版本为公版，仅限个人用户消费使用，不可用于商业服务用途，对于违规使用产生的后果及风险，腾讯音乐保留追究的权利。&lt;/h3&gt;&lt;/div&gt;&lt;/div&gt;&lt;div class="popup__ft"&gt;&lt;a class="upload_btns__item mod_btn_green js_stat_down js_close_tips" data-type="10" href="https://dldir1.qq.com/music/qqmusiccar/10049404-qqmusiccar-3.10.0.6-80dc5dd2bd_commonMv_full-release-signed.apk" target="_blank"&gt;确认并下载&lt;/a&gt;&lt;a class="upload_btns__item mod_btn js_close_tips" href="javascript:;"&gt;取消&lt;/a&gt;&lt;/div&gt;&lt;/div&gt;
+        &lt;/div&gt;，再点击dialog的确定才开始下载车载软件，抓取Android 车载的下载url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://lanshares.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lanshare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="download-card"&gt;
+                &lt;img class="system-icon" src="/system/android-fill.png" alt="Android"&gt;
+                &lt;h3 class="system-name"&gt;Android&lt;/h3&gt;
+                &lt;p class="version-info"&gt;版本: V1.2.8&lt;/p&gt;
+                &lt;p class="version-info"&gt;下载次数: 103299&lt;/p&gt;
+                &lt;a href="http://fgsqw.com/release/LANShare_1.2.8.apk?device=web&amp;amp;type=android?device=web&amp;amp;type=android" class="download-btn"&gt;立即下载&lt;/a&gt;
+            &lt;/div&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.estrongs.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES文件浏览器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a data-v-5c823f7d="" href="http://s.duapps.com/apks/own/ESFileExplorer-cn.apk" target="_blank" class="button gap-left"&gt;&lt;i data-v-5c823f7d="" class="icon-market icon-android"&gt;&lt;/i&gt;
+            Android
+          &lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.shafa.com/car</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙发管家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>车机版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.dangbei.com/chezai/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当贝市场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;div class="dbczContainer-content_links_downloadBtn"&gt;
+&lt;a href="https://app.qingyingyong.net/down/20250206/dbappstore_car2_1.0.3_dangbei.apk" target="_blank"&gt;立即下载&lt;/a&gt;
+&lt;/div&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a class="download" href="//zero.shafa.com/file/pad_webwww/shafa_market/latest"&gt;立即下载&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快马市场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.chaui.cn/KMStore/index.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a class="download center" href="javascript:;;" onclick="download_client()"&gt;免费下载&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统工具</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +618,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF334155"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -544,7 +633,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -567,12 +656,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -589,6 +689,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -870,12 +980,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I27"/>
+  <dimension ref="B1:I33"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="4" max="4" width="45.5546875" customWidth="1"/>
-    <col min="5" max="5" width="60.21875" customWidth="1"/>
+    <col min="5" max="5" width="60.21875" style="6" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" customWidth="1"/>
     <col min="8" max="8" width="11.44140625" customWidth="1"/>
   </cols>
@@ -891,14 +1001,14 @@
       <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -911,14 +1021,14 @@
       <c r="D3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>55</v>
+      <c r="E3" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -931,14 +1041,14 @@
       <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
-        <v>56</v>
+      <c r="E4" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -953,19 +1063,19 @@
       <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
-        <v>57</v>
+      <c r="E5" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>0</v>
       </c>
@@ -975,19 +1085,19 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>58</v>
+      <c r="E6" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
@@ -997,14 +1107,14 @@
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>59</v>
+      <c r="E7" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1020,16 +1130,16 @@
         <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1039,14 +1149,14 @@
       <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>61</v>
+      <c r="E9" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="152.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1060,13 +1170,13 @@
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1079,14 +1189,14 @@
       <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
-        <v>63</v>
+      <c r="E11" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1099,17 +1209,17 @@
       <c r="D12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E12" t="s">
-        <v>64</v>
+      <c r="E12" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="193.8" thickBot="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1119,17 +1229,17 @@
       <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>66</v>
+      <c r="E13" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="193.8" thickBot="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1139,17 +1249,17 @@
       <c r="D14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>65</v>
+      <c r="E14" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
@@ -1159,17 +1269,17 @@
       <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>67</v>
+      <c r="E15" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1179,17 +1289,17 @@
       <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>68</v>
+      <c r="E16" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1199,14 +1309,14 @@
       <c r="D17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>69</v>
+      <c r="E17" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1219,14 +1329,14 @@
       <c r="D18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E18" t="s">
-        <v>47</v>
+      <c r="E18" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
@@ -1237,16 +1347,16 @@
         <v>21</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
         <v>47</v>
       </c>
+      <c r="E19" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1260,10 +1370,10 @@
         <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -1277,13 +1387,13 @@
         <v>39</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1296,14 +1406,14 @@
       <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E22" t="s">
-        <v>71</v>
+      <c r="E22" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1316,17 +1426,17 @@
       <c r="D23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E23" t="s">
-        <v>72</v>
+      <c r="E23" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="318" thickBot="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
@@ -1336,14 +1446,14 @@
       <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>73</v>
+      <c r="E24" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1356,14 +1466,14 @@
       <c r="D25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E25" t="s">
-        <v>47</v>
+      <c r="E25" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1376,14 +1486,14 @@
       <c r="D26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E26" t="s">
-        <v>74</v>
+      <c r="E26" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1396,15 +1506,118 @@
       <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
-      </c>
+      <c r="E28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="69" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G33" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1433,6 +1646,12 @@
     <hyperlink ref="D14" r:id="rId22" xr:uid="{DFF5A280-0D05-4961-AD9D-37E607F7B48C}"/>
     <hyperlink ref="D23" r:id="rId23" xr:uid="{4414EC61-0C2C-4D17-AD0F-0E8757CF8F0C}"/>
     <hyperlink ref="D16" r:id="rId24" xr:uid="{AC92265F-D2BA-49B5-A4D3-E1D59C1F77FE}"/>
+    <hyperlink ref="D5" r:id="rId25" xr:uid="{7D3F517E-7F78-42AF-B155-CCD4B3383EE4}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{ADE8E0EF-8AC2-4B47-8FE9-085C25CFD818}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{7C21FEAF-48BA-477E-BCD8-B3F05EBC4480}"/>
+    <hyperlink ref="D30" r:id="rId28" xr:uid="{38A3E815-3446-401C-AD39-408F557A67C8}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{B6B80689-9DDD-4188-9329-2C37CB6CEC3E}"/>
+    <hyperlink ref="D32" r:id="rId30" xr:uid="{8608C1D6-73D0-4B71-B9DB-CC8156247E22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
